--- a/outputs/36097.xlsx
+++ b/outputs/36097.xlsx
@@ -527,7 +527,7 @@
         <v>34600</v>
       </c>
       <c r="H3" s="7" t="n">
-        <f aca="false">IF(F3&lt;0,E3+F3,IF(F3&lt;C3,F3,C3-E3))</f>
+        <f aca="false">IF(F3&lt;0,E3-F3,IF(F3&lt;C3,F3,C3-E3))</f>
         <v>4000</v>
       </c>
     </row>
@@ -555,7 +555,7 @@
         <v>8100</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">IF(F4&lt;0,E4+F4,IF(F4&lt;C4,F4,C4-E4))</f>
+        <f aca="false">IF(F4&lt;0,E4-F4,IF(F4&lt;C4,F4,C4-E4))</f>
         <v>2250</v>
       </c>
     </row>
@@ -583,7 +583,7 @@
         <v>800</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">IF(F5&lt;0,E5+F5,IF(F5&lt;C5,F5,C5-E5))</f>
+        <f aca="false">IF(F5&lt;0,E5-F5,IF(F5&lt;C5,F5,C5-E5))</f>
         <v>800</v>
       </c>
     </row>
@@ -611,8 +611,8 @@
         <v>100</v>
       </c>
       <c r="H6" s="7" t="n">
-        <f aca="false">IF(F6&lt;0,E6+F6,IF(F6&lt;C6,F6,C6-E6))</f>
-        <v>-50</v>
+        <f aca="false">IF(F6&lt;0,E6-F6,IF(F6&lt;C6,F6,C6-E6))</f>
+        <v>350</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -642,7 +642,7 @@
       </c>
       <c r="H7" s="9" t="n">
         <f aca="false">SUM(H3:H6)</f>
-        <v>7000</v>
+        <v>7400</v>
       </c>
     </row>
   </sheetData>
